--- a/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.871</v>
+        <v>0.84</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7297</v>
+        <v>0.5676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8462</v>
+        <v>0.8571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6207</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9593</v>
+        <v>0.9881</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8697</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8519</v>
+        <v>0.7619</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6818</v>
+        <v>0.8333</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8239</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5556</v>
+        <v>0.9048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2174</v>
+        <v>0.2353</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.85</v>
+        <v>0.8125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8095</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +664,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8333</v>
+        <v>0.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -686,16 +686,16 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.871</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="9">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7297</v>
+        <v>0.5676</v>
       </c>
     </row>
     <row r="10">
@@ -880,22 +880,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -908,22 +908,22 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -936,22 +936,22 @@
         <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -964,22 +964,22 @@
         <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
         <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -992,22 +992,22 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -1020,22 +1020,22 @@
         <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>21</v>
-      </c>
-      <c r="E7" t="n">
-        <v>23</v>
-      </c>
-      <c r="F7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,258 +1185,258 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M04_AU23</t>
+          <t>CF_M04_AU25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7707000000000001</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Data Layer (Frontend)</t>
-        </is>
-      </c>
+        <v>0.7603</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Handles data access, including backend calls, data transformation, and concrete repository implementations.</t>
+          <t>El back-end està implementat utilitzant Django i segueix el patró d’Arquitectura Hexagonal [...] Dins del back-end es poden distingir clarament tres capes principals: Capa de Domini [...] Capa d’Aplicació [...] Capa d’Infraestructura.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02', 'AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>backend, domain layer, application layer, infrastructure layer</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
+          <t>In the back-end, HTTP requests received by Django views are delegated to the corresponding use cases, which encapsulate the business logic and use repositories to access the database or external services.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
+          <t>CF_M04_AU04, CF_M04_AU10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M04_AU23</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>CF_M04_AU25</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>backend, database</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M04_AU25</t>
+          <t>CF_M04_P04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7832</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>0.7858000000000001</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cubit</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>The back-end uses MySQL for data persistence, managed through the Django ORM.</t>
+          <t>A pattern used for state management and business logic in the Flutter frontend.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_11']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>backend, mysql</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>AU_06</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Bloc/Cubit</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>In the back-end, HTTP requests received by Django views are delegated to the corresponding use cases, which encapsulate the business logic and use repositories to access the database or external services.</t>
+          <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M04_AU04, CF_M04_AU10</t>
+          <t>CF_M04_AU01</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M04_AU25</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>backend, database</t>
-        </is>
-      </c>
+          <t>CF_M04_P04</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M04_AU22</t>
+          <t>CF_M04_AU15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Domain Layer (Frontend)</t>
-        </is>
-      </c>
+        <v>0.9144</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Contains business logic, use cases, entities, and repository interfaces.</t>
+          <t>El sistema integra diversos serveis externs a través del back-end, com ara serveis d’intel·ligència artificial (Gemini o ChatGPT) i serveis d’autenticació.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02', 'AU_07', 'AU_08']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>backend, authentication service, ai service</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Domain: contains the business logic, with use cases, entities and repositories defined as interfaces.</t>
+          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
+          <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M04_AU22</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>CF_M04_AU15</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>frontend, gemini</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M04_AU15</t>
+          <t>CF_M04_AU29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7893</v>
+        <v>0.9443</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
@@ -1455,28 +1455,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The backend sends the review context to the artificial intelligence service, in this case Gemini, to generate a response suggestion.</t>
+          <t>La comunicació entre el front-end i el back-end es realitza mitjançant una API REST, utilitzant missatges en format JSON tant per a les peticions com per a les respostes.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_15']</t>
+          <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>backend, ai service</t>
+          <t>frontend, backend</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
+          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1495,99 +1495,95 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
+          <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M04_AU15</t>
+          <t>CF_M04_AU29</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>frontend, gemini</t>
+          <t>frontend, backend</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M04_AU06</t>
+          <t>CF_M04_P08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8436</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Clean Architecture</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Communication protocol used between frontend and backend.</t>
+          <t>The frontend follows the principles of Clean Architecture, applied strictly to organize code into layers.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['AU_21']</t>
-        </is>
-      </c>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Clean Architecture</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Communication between the front-end and the back-end is done through a REST API</t>
+          <t>The front-end is implemented with Flutter and follows a structure based on the principles of Clean Architecture, strictly applied.</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
+          <t>CF_M04_AU01</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M04_AU06</t>
+          <t>CF_M04_P08</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1595,94 +1591,94 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M04_AU16</t>
+          <t>CF_M04_AU07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8521</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Domain Layer</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The back-end integrates various external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
+          <t>Contains the purest business logic of the system, as well as domain models and repository interfaces.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_15', 'AU_18']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>backend, ai service, authentication service</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Domain Layer</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Integrations with external services such as Gemini, ChatGPT orFirebase.</t>
+          <t>Domain Layer: contains the purest business logic of the system, as well as the domain models and repositories interfaces.</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CF_M04_AU09, CF_M04_AU013, CF_M04_AU14</t>
+          <t>CF_M04_P01</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M04_AU16</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>infrastructure layer, gemini</t>
-        </is>
-      </c>
+          <t>CF_M04_AU07</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M04_AU08</t>
+          <t>CF_M04_AU11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1691,26 +1687,26 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.914</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Application Layer (Backend)</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Includes system use cases that orchestrate business logic and define operation flows.</t>
+          <t>Relational database management system used for data persistence.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1721,23 +1717,23 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Application Layer</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Application Layer: includes the system use cases, which orchestrate the business logic and define the flow of operations</t>
+          <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1745,13 +1741,13 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M04_P01</t>
+          <t>CF_M04_AU10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M04_AU08</t>
+          <t>CF_M04_AU11</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1759,12 +1755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M04_AU09</t>
+          <t>CF_M04_AU06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1773,21 +1769,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9141</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Infrastructure Layer (Backend)</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Responsible for interaction with the exterior, including Django HTTP views, ORM repositories, and external service adapters.</t>
+          <t>La comunicació entre el front-end i el back-end es realitza mitjançant una API REST</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1797,29 +1793,29 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Infrastructure Layer</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Infrastructure Layer: This is responsible for interaction with the outside world.</t>
+          <t>Communication between the front-end and the back-end is done through a REST API</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1827,13 +1823,13 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M04_P01</t>
+          <t>CF_M04_AU29</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M04_AU09</t>
+          <t>CF_M04_AU06</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1841,12 +1837,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M04_AU07</t>
+          <t>CF_M04_AU09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1855,11 +1851,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9246</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Domain Layer (Backend)</t>
+          <t>Infrastructure Layer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1869,12 +1865,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Contains the purest business logic, domain models, and repository interfaces, independent of Django or the database.</t>
+          <t>Responsible for interaction with the outside, including Django HTTP views, repositories, and adapters for external services.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1885,13 +1881,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Domain Layer</t>
+          <t>Infrastructure Layer</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1901,7 +1897,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Domain Layer: contains the purest business logic of the system, as well as the domain models and repositories interfaces.</t>
+          <t>Infrastructure Layer: This is responsible for interaction with the outside world.</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1915,7 +1911,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M04_AU07</t>
+          <t>CF_M04_AU09</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1923,12 +1919,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M04_AU02</t>
+          <t>CF_M04_AU18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1937,67 +1933,63 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9486</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Presentation Layer (Frontend)</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Manages the application state and communication with the user interface using Bloc/Cubit.</t>
+          <t>Specialized service responsible for creating and sending OTP codes for delegated login.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
+          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>CF_M04_AU01</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M04_AU02</t>
+          <t>CF_M04_AU18</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -2005,181 +1997,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
+          <t>CF_M04_AU17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The frontend communicates with the backend to obtain or modify information. [...] The communication between the front-end and the back-end is performed through a REST API, using JSON format messages for both requests and responses.</t>
+          <t>Communication protocol used between frontend and backend.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>55,70</t>
+          <t>55, 70</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_01', 'AU_02']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>frontend, backend</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
+          <t>Communication is done through an HTTP-based REST API. Data is exchanged in JSON format, using standard HTTP methods such as GET and POST.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M04_AU01, CF_M04_AU04</t>
+          <t>CF_M04_AU06</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>frontend, backend</t>
-        </is>
-      </c>
+          <t>CF_M04_AU17</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M04_AU19</t>
+          <t>CF_M04_P06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9688</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Factory Pattern</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The backend delegates the generation of the OTP code to a specialized authentication service.</t>
+          <t>Used to dynamically instantiate artificial intelligence services according to the system configuration.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_18']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>backend, authentication service</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Factory Pattern</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
+          <t>Factory Pattern: Used to dynamically instantiate intelligence services artificial according to the system configuration.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M04_AU04, CF_M04_AU18</t>
+          <t>CF_M04_AU04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M04_AU19</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>backend, authentication service</t>
-        </is>
-      </c>
+          <t>CF_M04_P06</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
+          <t>CF_M04_AU04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2187,59 +2179,55 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Clean Architecture</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The front-end is implemented with Flutter and follows an structure based on the principles of Clean Architecture, applied strictly.</t>
+          <t>The server-side software responsible for processing user requests, implemented using Django.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>54, 55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Clean Architecture</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>The front-end is implemented with Flutter and follows a structure based on the principles of Clean Architecture, strictly applied.</t>
+          <t>The back-end is implemented using Django and follows the Hexagonal Architecture pattern (Ports and Adapters), which allows separating business logic from framework and infrastructure technologies.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CF_M04_AU01</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
+          <t>CF_M04_AU04</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2247,12 +2235,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M04_AU11</t>
+          <t>CF_M04_AU08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2265,49 +2253,49 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Application Layer</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Relational database management system used for data persistence.</t>
+          <t>Includes the system's use cases, which orchestrate business logic and define the flow of operations.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55, 65</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_23']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Application Layer</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
+          <t>Application Layer: includes the system use cases, which orchestrate the business logic and define the flow of operations</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2315,13 +2303,13 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M04_AU10</t>
+          <t>CF_M04_P01</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M04_AU11</t>
+          <t>CF_M04_AU08</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2329,12 +2317,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M04_AU27</t>
+          <t>CF_M04_AU01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2347,59 +2335,55 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Used for complementary functionalities like notifications.</t>
+          <t>The mobile application developed with Flutter, which acts as the presentation layer.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['AU_02']</t>
-        </is>
-      </c>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Firebase for complementary functionalities (notifications, services associated).</t>
+          <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M04_AU27</t>
+          <t>CF_M04_AU01</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2407,12 +2391,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M04_AU17</t>
+          <t>CF_M04_AU05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2425,7 +2409,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Django</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2435,29 +2419,29 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Protocol used for REST API communication.</t>
+          <t>Framework used for the construction of the REST API in the backend.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_12', 'AU_21']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Django</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2467,21 +2451,21 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Communication is done through an HTTP-based REST API. Data is exchanged in JSON format, using standard HTTP methods such as GET and POST.</t>
+          <t>The back-end is implemented using Django and follows the Hexagonal Architecture pattern (Ports and Adapters), which allows separating business logic from framework and infrastructure technologies.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M04_AU06</t>
+          <t>CF_M04_AU04</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M04_AU17</t>
+          <t>CF_M04_AU05</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2489,12 +2473,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M04_AU18</t>
+          <t>CF_M04_AU14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2507,22 +2491,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>External service for user authentication.</t>
+          <t>External AI service integrated into the system.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2533,13 +2517,13 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2549,17 +2533,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
+          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M04_AU18</t>
+          <t>CF_M04_AU14</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2567,12 +2551,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M04_P06</t>
+          <t>CF_M04_P05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2585,7 +2569,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Factory Pattern</t>
+          <t>Repository Pattern</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2595,7 +2579,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Used to dynamically instantiate artificial intelligence services according to system configuration.</t>
+          <t>Isolates data access and simplifies the use of the ORM in use cases.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2605,19 +2589,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Factory Pattern</t>
+          <t>Repository Pattern</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2627,7 +2611,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Factory Pattern: Used to dynamically instantiate intelligence services artificial according to the system configuration.</t>
+          <t>Repository Pattern: Isolates access to data and simplifies the use of the ORM in cases of use.</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2635,13 +2619,13 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M04_AU04</t>
+          <t>CF_M04_AU09</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M04_P06</t>
+          <t>CF_M04_P05</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2649,12 +2633,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M04_AU04</t>
+          <t>CF_M04_AU13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2667,45 +2651,49 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The server-side software responsible for business logic, data persistence, and integration with external services.</t>
+          <t>External AI service integrated into the system.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>55, 56</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['AU_08']</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>The back-end is implemented using Django and follows the Hexagonal Architecture pattern (Ports and Adapters), which allows separating business logic from framework and infrastructure technologies.</t>
+          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2715,7 +2703,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M04_AU04</t>
+          <t>CF_M04_AU13</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2723,17 +2711,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M04_AU01</t>
+          <t>CF_M04_P01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2741,622 +2729,146 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Hexagonal Architecture</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The mobile application developed with Flutter that acts as the presentation layer, managing the graphical interface, navigation, and user interaction.</t>
+          <t>The backend follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55, 64</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Hexagonal Architecture</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>CF_M04_AU01</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CF_M04_P04</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Bloc/Cubit</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Pattern used for state management and business logic in the frontend.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['P_02']</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Bloc/Cubit</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>CF_M04_AU01</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>CF_M04_P04</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CF_M04_AU05</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Django</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Backend framework used for building the REST API.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['AU_02']</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Django</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>The back-end is implemented using Django and follows the Hexagonal Architecture pattern (Ports and Adapters), which allows separating business logic from framework and infrastructure technologies.</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>CF_M04_AU04</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>CF_M04_AU05</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CF_M04_AU14</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Gemini</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AI service provider used for Cintia functionality.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['AU_15', 'AU_25']</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Gemini</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>CF_M04_AU14</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M04_P05</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Repository Pattern</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Isolates data access and simplifies the use of the ORM in use cases.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Repository Pattern</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Repository Pattern: Isolates access to data and simplifies the use of the ORM in cases of use.</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>CF_M04_AU09</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CF_M04_P05</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CF_M04_AU13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ChatGPT</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AI service provider used for Cintia functionality.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['AU_15']</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>ChatGPT</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>CF_M04_AU13</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CF_M04_P01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Hexagonal Architecture</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>The back-end is implemented using Django and follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Hexagonal Architecture</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
         <is>
           <t>The back-end is implemented using Django and follows the Hexagonal Architecture pattern
 (Ports and Adapters), which allows separating business logic from framework and infrastructure
 technologies. Within the back-end, three layers can be clearly distinguished.</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="P21" t="n">
         <v>55</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Flutter</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Framework used for cross-platform mobile application development.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Framework used for the development of the mobile application.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>54, 56</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Flutter</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="P22" t="n">
         <v>54</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>CF_M04_AU01, CF_M04_AU03</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3417,71 +2929,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>AI Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data format used for requests and responses.</t>
+          <t>External service used for generating response suggestions for reviews.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
+          <t>CF_M04_AU15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.7808</v>
+        <v>0.7329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AI Service</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>infrastructure layer, mysql</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>External service for generating review responses.</t>
+          <t>La persistència de les dades es realitza mitjançant una base de dades relacional MySQL, gestionada a través de l’ORM de Django.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M04_AU15</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>CF_M04_P07</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0.7329</v>
+        <v>0.7435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3491,63 +3007,59 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Google OAuth 2.0</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Authentication provider used for user login.</t>
+          <t>Les dades s’intercanvien en format JSON, utilitzant mètodes HTTP estàndard com GET i POST.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M04_AU26</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Google Login</t>
-        </is>
-      </c>
+          <t>CF_M04_AU29</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.795</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dependency Inversion (DIP)</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The domain defines interfaces that are implemented by the infrastructure.</t>
+          <t>The system follows a client-server architecture where the mobile application acts as the frontend and the server processes requests.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M04_P02</t>
+          <t>CF_M04_AU17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hierarchical model</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6261</v>
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>
@@ -3561,7 +3073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,115 +3121,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M04_AU10</t>
+          <t>CF_M04_AU02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Component </t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
+          <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Application Layer</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7872</v>
+        <v>0.8548</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M04_AU12</t>
+          <t>CF_M04_AU10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>application layer, domain layer, infrastructure layer</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Component </t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>It acts as an intermediary between the domain and the infrastructure.</t>
+          <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Domain Layer (Frontend)</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7644</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M04_AU20</t>
+          <t>CF_M04_AU12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>application layer, domain layer, infrastructure layer</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Users: Application customers who use the new features and provide feedback.</t>
+          <t>It acts as an intermediary between the domain and the infrastructure.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Domain Layer</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.718</v>
+        <v>0.7792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M04_AU21</t>
+          <t>CF_M04_AU16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3728,104 +3240,100 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>frontend</t>
+          <t>infrastructure layer, gemini</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
+          <t>Integrations with external services such as Gemini, ChatGPT orFirebase.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.7078</v>
+        <v>0.8525</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M04_AU24</t>
+          <t>CF_M04_AU19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>backend, authentication service</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
+          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Presentation Layer (Frontend)</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9486</v>
+        <v>0.7536</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M04_AU26</t>
+          <t>CF_M04_AU20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Google Login</t>
+          <t>User</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Authentication services, such as Google login.</t>
+          <t>Users: Application customers who use the new features and provide feedback.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Google OAuth 2.0</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.795</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M04_AU28</t>
+          <t>CF_M04_AU21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3836,130 +3344,346 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>data, backend</t>
+          <t>frontend</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
+          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Data Layer (Frontend)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7814</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M04_P02</t>
+          <t>CF_M04_AU22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hierarchical model</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
+          <t>Domain: contains the business logic, with use cases, entities and repositories defined as interfaces.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hexagonal Architecture</t>
+          <t>Domain Layer</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6627</v>
+        <v>0.8591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M04_P03</t>
+          <t>CF_M04_AU23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modular architecture</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
+          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hexagonal Architecture</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6897</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M04_P07</t>
+          <t>CF_M04_AU24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Application Layer</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8548</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M04_AU26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Google Login</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Authentication services, such as Google login.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6734</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M04_AU27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Firebase</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Firebase for complementary functionalities (notifications, services associated).</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6827</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M04_AU28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>data, backend</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M04_P02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hierarchical model</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Domain Layer</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6816</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CF_M04_P03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Modular architecture</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hexagonal Architecture</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF_M04_P07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>0.7118</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.7435</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.5676</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6774</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6207</v>
       </c>
       <c r="D3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9881</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.375</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.873</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7603</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_02', 'AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_16</t>
@@ -1233,7 +1245,6 @@
           <t>backend, domain layer, application layer, infrastructure layer</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M04_AU04, CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M04_AU25</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Bloc/Cubit</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M04_P04</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1365,7 +1371,6 @@
       <c r="D4" t="n">
         <v>0.9144</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1386,7 +1391,6 @@
           <t>['AU_02', 'AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_18</t>
@@ -1397,7 +1401,6 @@
           <t>backend, authentication service, ai service</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1416,7 +1419,6 @@
           <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M04_AU15</t>
@@ -1447,7 +1449,6 @@
       <c r="D5" t="n">
         <v>0.9443</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1468,7 +1469,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_15</t>
@@ -1479,7 +1479,6 @@
           <t>frontend, backend</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1498,7 +1497,6 @@
           <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M04_AU29</t>
@@ -1549,14 +1547,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Clean Architecture</t>
@@ -1580,13 +1575,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1632,13 +1625,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Domain Layer</t>
@@ -1662,13 +1653,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M04_AU07</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1714,13 +1703,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -1744,13 +1731,11 @@
           <t>CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M04_AU11</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1796,13 +1781,11 @@
           <t>['AU_15']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>REST</t>
@@ -1826,13 +1809,11 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1878,13 +1859,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Infrastructure Layer</t>
@@ -1908,13 +1887,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1960,13 +1937,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Authentication Service</t>
@@ -1985,14 +1960,11 @@
       <c r="P11" t="n">
         <v>68</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M04_AU18</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2038,13 +2010,11 @@
           <t>['AU_15']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2068,13 +2038,11 @@
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M04_AU17</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2120,13 +2088,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Factory Pattern</t>
@@ -2150,13 +2116,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M04_P06</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2197,14 +2161,11 @@
           <t>54, 55</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -2223,14 +2184,11 @@
       <c r="P14" t="n">
         <v>55</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2276,13 +2234,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Application Layer</t>
@@ -2306,13 +2262,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M04_AU08</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2353,14 +2307,11 @@
           <t>54</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -2379,14 +2330,11 @@
       <c r="P16" t="n">
         <v>54</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2432,13 +2380,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Django</t>
@@ -2462,13 +2408,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M04_AU05</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2514,13 +2458,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gemini</t>
@@ -2539,14 +2481,11 @@
       <c r="P18" t="n">
         <v>55</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M04_AU14</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2592,13 +2531,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Repository Pattern</t>
@@ -2622,13 +2559,11 @@
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M04_P05</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2674,13 +2609,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>ChatGPT</t>
@@ -2699,14 +2632,11 @@
       <c r="P20" t="n">
         <v>55</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M04_AU13</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2747,14 +2677,11 @@
           <t>55, 64</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Hexagonal Architecture</t>
@@ -2780,13 +2707,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2832,13 +2757,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Flutter</t>
@@ -2862,13 +2785,11 @@
           <t>CF_M04_AU01, CF_M04_AU03</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2942,7 +2863,6 @@
           <t>AI Service</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>External service used for generating response suggestions for reviews.</t>
@@ -2953,7 +2873,6 @@
           <t>CF_M04_AU15</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.7329</v>
       </c>
@@ -2969,7 +2888,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>infrastructure layer, mysql</t>
@@ -3010,7 +2928,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Les dades s’intercanvien en format JSON, utilitzant mètodes HTTP estàndard com GET i POST.</t>
@@ -3021,7 +2938,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7808</v>
       </c>
@@ -3042,7 +2958,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>The system follows a client-server architecture where the mobile application acts as the frontend and the server processes requests.</t>
@@ -3134,7 +3049,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
@@ -3170,7 +3084,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
@@ -3201,7 +3114,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>application layer, domain layer, infrastructure layer</t>
@@ -3237,7 +3149,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>infrastructure layer, gemini</t>
@@ -3253,7 +3164,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.8525</v>
       </c>
@@ -3269,7 +3179,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>backend, authentication service</t>
@@ -3310,7 +3219,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Users: Application customers who use the new features and provide feedback.</t>
@@ -3341,7 +3249,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>frontend</t>
@@ -3382,7 +3289,6 @@
           <t>Domain</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Domain: contains the business logic, with use cases, entities and repositories defined as interfaces.</t>
@@ -3418,7 +3324,6 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
@@ -3454,7 +3359,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
@@ -3490,7 +3394,6 @@
           <t>Google Login</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Authentication services, such as Google login.</t>
@@ -3526,7 +3429,6 @@
           <t>Firebase</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Firebase for complementary functionalities (notifications, services associated).</t>
@@ -3557,7 +3459,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -3598,7 +3499,6 @@
           <t>Hierarchical model</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
@@ -3634,7 +3534,6 @@
           <t>Modular architecture</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
@@ -3670,7 +3569,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
@@ -3681,7 +3579,6 @@
           <t>AU_17</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0.7435</v>
       </c>
